--- a/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados perfiles halpha 2018 priorizando el sector naranja.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados perfiles halpha 2018 priorizando el sector naranja.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sector_naranja</t>
+          <t>Sector naranja</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>sector_naranja</t>
+          <t>Sector naranja</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sector_naranja</t>
+          <t>Sector naranja</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>halpha</t>
+          <t>Hα</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>halpha</t>
+          <t>Hα</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>halpha</t>
+          <t>Hα</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sector_naranja</t>
+          <t>Sector naranja</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sector_naranja</t>
+          <t>Sector naranja</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sector_naranja</t>
+          <t>Sector naranja</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sector_naranja</t>
+          <t>Sector naranja</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sector_naranja</t>
+          <t>Sector naranja</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sector_naranja</t>
+          <t>Sector naranja</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>halpha</t>
+          <t>Hα</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>halpha</t>
+          <t>Hα</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>halpha</t>
+          <t>Hα</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sector_naranja</t>
+          <t>Sector naranja</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sector_naranja</t>
+          <t>Sector naranja</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sector_naranja</t>
+          <t>Sector naranja</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sector_naranja</t>
+          <t>Sector naranja</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sector_naranja</t>
+          <t>Sector naranja</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sector_naranja</t>
+          <t>Sector naranja</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sector_naranja</t>
+          <t>Sector naranja</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>sector_naranja</t>
+          <t>Sector naranja</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sector_naranja</t>
+          <t>Sector naranja</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sector_naranja</t>
+          <t>Sector naranja</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>sector_naranja</t>
+          <t>Sector naranja</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sector_naranja</t>
+          <t>Sector naranja</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
